--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/006203-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/006203-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2F1319B-BECA-449D-9CE6-65B581B640C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F5561D1-2FD2-4566-BBE5-6330A8EA9D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{FC2E7151-582E-44EA-A399-54D905AB5EBC}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{FA18DEF2-02D3-4FA5-A625-597CEB885E23}"/>
   </bookViews>
   <sheets>
     <sheet name="006203-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1573,25 +1573,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9173D700-805C-47BD-89E9-C7F438A7AB08}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2167FAC-B9D0-475E-A49F-0A824A53CD1D}">
   <dimension ref="A1:R42"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1619,7 +1619,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1649,7 +1649,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1695,7 +1695,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1745,7 +1745,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1799,7 +1799,7 @@
         <v>2.77</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1825,7 +1825,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1881,7 +1881,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1935,7 +1935,7 @@
         <v>2.63</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1991,7 +1991,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2047,7 +2047,7 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="51">
         <v>2024</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>3.76</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>27</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>27</v>
       </c>
@@ -2213,7 +2213,7 @@
         <v>2.79</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="49">
         <v>2023</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>3.55</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>27</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>27</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>2.16</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="51">
         <v>2022</v>
       </c>
@@ -2433,7 +2433,7 @@
         <v>3.47</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>27</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>1.48</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>27</v>
       </c>
@@ -2545,7 +2545,7 @@
         <v>1.99</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="49">
         <v>2021</v>
       </c>
@@ -2599,7 +2599,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2655,7 +2655,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
@@ -2711,7 +2711,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51">
         <v>2020</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>27</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>27</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>3.22</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="49">
         <v>2019</v>
       </c>
@@ -2931,7 +2931,7 @@
         <v>3.44</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
         <v>27</v>
       </c>
@@ -2987,7 +2987,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
         <v>27</v>
       </c>
@@ -3043,7 +3043,7 @@
         <v>2.41</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="51">
         <v>2018</v>
       </c>
@@ -3097,7 +3097,7 @@
         <v>2.93</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>27</v>
       </c>
@@ -3153,7 +3153,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>27</v>
       </c>
@@ -3209,7 +3209,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="49">
         <v>2017</v>
       </c>
@@ -3263,7 +3263,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
         <v>27</v>
       </c>
@@ -3319,7 +3319,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
         <v>27</v>
       </c>
@@ -3375,7 +3375,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="51">
         <v>2016</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>27</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="49">
         <v>2015</v>
       </c>
@@ -3539,7 +3539,7 @@
         <v>3.29</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="51">
         <v>2014</v>
       </c>
@@ -3593,7 +3593,7 @@
         <v>2.29</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="49">
         <v>2013</v>
       </c>
@@ -3647,7 +3647,7 @@
         <v>3.09</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="51">
         <v>2012</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>2.81</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="49">
         <v>2011</v>
       </c>
@@ -3755,7 +3755,7 @@
         <v>3.28</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="51" t="s">
         <v>62</v>
       </c>
